--- a/outputs/Goat_tukey_classification_matrix.xlsx
+++ b/outputs/Goat_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5060" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5060" uniqueCount="267">
   <si>
     <t>2008 Jan</t>
   </si>
@@ -749,6 +749,9 @@
   </si>
   <si>
     <t>Alert</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>13%</t>
@@ -2509,13 +2512,13 @@
         <v>243</v>
       </c>
       <c r="HJ2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HK2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="HL2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:220">
@@ -3171,13 +3174,13 @@
         <v>243</v>
       </c>
       <c r="HJ3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="HK3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="HL3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:220">
@@ -3326,7 +3329,7 @@
         <v>242</v>
       </c>
       <c r="AW4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AX4" t="s">
         <v>244</v>
@@ -3833,13 +3836,13 @@
         <v>243</v>
       </c>
       <c r="HJ4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="HK4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="HL4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:220">
@@ -4495,13 +4498,13 @@
         <v>243</v>
       </c>
       <c r="HJ5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="HK5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="HL5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:220">
@@ -5157,13 +5160,13 @@
         <v>243</v>
       </c>
       <c r="HJ6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="HK6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="HL6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:220">
@@ -5819,13 +5822,13 @@
         <v>243</v>
       </c>
       <c r="HJ7" t="s">
+        <v>249</v>
+      </c>
+      <c r="HK7" t="s">
+        <v>263</v>
+      </c>
+      <c r="HL7" t="s">
         <v>248</v>
-      </c>
-      <c r="HK7" t="s">
-        <v>262</v>
-      </c>
-      <c r="HL7" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:220">
@@ -6481,13 +6484,13 @@
         <v>243</v>
       </c>
       <c r="HJ8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="HK8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="HL8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:220">
@@ -7143,13 +7146,13 @@
         <v>243</v>
       </c>
       <c r="HJ9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="HK9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HL9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:220">
@@ -7805,13 +7808,13 @@
         <v>243</v>
       </c>
       <c r="HJ10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="HK10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="HL10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:220">
@@ -8467,13 +8470,13 @@
         <v>243</v>
       </c>
       <c r="HJ11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="HK11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HL11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:220">
@@ -9129,13 +9132,13 @@
         <v>243</v>
       </c>
       <c r="HJ12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="HK12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="HL12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" spans="1:220">
@@ -9791,13 +9794,13 @@
         <v>243</v>
       </c>
       <c r="HJ13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="HK13" t="s">
+        <v>259</v>
+      </c>
+      <c r="HL13" t="s">
         <v>258</v>
-      </c>
-      <c r="HL13" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:220">
@@ -10453,13 +10456,13 @@
         <v>243</v>
       </c>
       <c r="HJ14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="HK14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="HL14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" spans="1:220">
@@ -11115,13 +11118,13 @@
         <v>243</v>
       </c>
       <c r="HJ15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="HK15" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HL15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:220">
@@ -11231,10 +11234,10 @@
         <v>244</v>
       </c>
       <c r="AJ16" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AK16" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AL16" t="s">
         <v>242</v>
@@ -11777,13 +11780,13 @@
         <v>243</v>
       </c>
       <c r="HJ16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="HK16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="HL16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:220">
@@ -11854,13 +11857,13 @@
         <v>242</v>
       </c>
       <c r="W17" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="X17" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Y17" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Z17" t="s">
         <v>242</v>
@@ -12439,13 +12442,13 @@
         <v>243</v>
       </c>
       <c r="HJ17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="HK17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="HL17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:220">
@@ -13101,13 +13104,13 @@
         <v>243</v>
       </c>
       <c r="HJ18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="HK18" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="HL18" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:220">
@@ -13763,13 +13766,13 @@
         <v>243</v>
       </c>
       <c r="HJ19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="HK19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HL19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:220">
@@ -14425,13 +14428,13 @@
         <v>243</v>
       </c>
       <c r="HJ20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="HK20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="HL20" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:220">
@@ -15087,13 +15090,13 @@
         <v>243</v>
       </c>
       <c r="HJ21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="HK21" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HL21" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" spans="1:220">
@@ -15749,13 +15752,13 @@
         <v>243</v>
       </c>
       <c r="HJ22" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="HK22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="HL22" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" spans="1:220">
@@ -16411,13 +16414,13 @@
         <v>243</v>
       </c>
       <c r="HJ23" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="HK23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="HL23" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Goat_tukey_classification_matrix.xlsx
+++ b/outputs/Goat_tukey_classification_matrix.xlsx
@@ -742,7 +742,7 @@
     <t>West Pokot</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
